--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-coverage.xlsx
@@ -280,7 +280,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-coverage.xlsx
@@ -372,7 +372,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -700,7 +700,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -879,7 +879,7 @@
     <t>Coverage.status</t>
   </si>
   <si>
-    <t>アクティブ|キャンセル|ドラフト|エラーに入った / active | cancelled | draft | entered-in-error</t>
+    <t>アクティブ|キャンセル|ドラフト|エラー入力 / active | cancelled | draft | entered-in-error</t>
   </si>
   <si>
     <t>The status of the resource instance.  
@@ -931,7 +931,7 @@
     <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-type|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -1091,7 +1091,7 @@
     <t>加入者と受益者（被保険者/対象当事者/患者）の関係。 / The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
+    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship|4.0.1</t>
   </si>
   <si>
     <t>C03</t>
@@ -1236,7 +1236,7 @@
     <t>ポリシー分類、例。グループ、プラン、クラスなど / The policy classifications, eg. Group, Plan, Class, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-class</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-class|4.0.1</t>
   </si>
   <si>
     <t>Coverage.class.value</t>
@@ -1373,7 +1373,7 @@
     <t>患者の自己負担が指定されているサービスの種類。 / The types of services to which patient copayments are specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type|4.0.1</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.id</t>
@@ -1564,7 +1564,7 @@
     <t>Coverage.costToBeneficiary.value[x]</t>
   </si>
   <si>
-    <t>Quantity {SimpleQuantity}
+    <t>Quantity {SimpleQuantity|4.0.1}
 Money</t>
   </si>
   <si>
@@ -1622,7 +1622,7 @@
     <t>部品からの例外の種類またはCopaysなどの財務義務の完全な価値。 / The types of exceptions from the part or full value of financial obligations such as copays.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception|4.0.1</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.exception.period</t>
@@ -1660,7 +1660,7 @@
     <t>Coverage.contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Contract)
+    <t xml:space="preserve">Reference(Contract|4.0.1)
 </t>
   </si>
   <si>
@@ -1986,17 +1986,17 @@
   <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.9296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="21.3984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="128.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="110.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2005,28 +2005,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="207.19140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.84375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="177.6328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.83203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.69140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="59.44921875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="51.2734375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="62.85546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="50.96484375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="43.95703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="53.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-coverage.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
